--- a/branches/master/StructureDefinition-mii-pr-icu-muv-herzfrequenz.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-muv-herzfrequenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T22:41:23+00:00</t>
+    <t>2026-09-15T14:01:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-icu-muv-herzfrequenz.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-muv-herzfrequenz.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T14:01:05+00:00</t>
+    <t>2026-09-15T17:45:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-icu-muv-herzfrequenz.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-muv-herzfrequenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T17:45:52+00:00</t>
+    <t>2026-09-15T20:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-icu-muv-herzfrequenz.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-muv-herzfrequenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T20:38:45+00:00</t>
+    <t>2026-09-16T05:15:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-icu-muv-herzfrequenz.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-muv-herzfrequenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T05:15:10+00:00</t>
+    <t>2026-09-16T08:10:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-icu-muv-herzfrequenz.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-muv-herzfrequenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T08:10:08+00:00</t>
+    <t>2026-09-17T08:26:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-icu-muv-herzfrequenz.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-muv-herzfrequenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T08:26:08+00:00</t>
+    <t>2026-09-17T12:53:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-icu-muv-herzfrequenz.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-muv-herzfrequenz.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3458" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3459" uniqueCount="533">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:53:08+00:00</t>
+    <t>2026-09-23T08:48:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -422,7 +422,7 @@
     <t>Observation.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+    <t xml:space="preserve">canonical(StructureDefinition)
 </t>
   </si>
   <si>
@@ -460,7 +460,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -484,7 +484,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -528,7 +528,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -628,7 +628,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
 </t>
   </si>
   <si>
@@ -707,7 +707,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:$this}
@@ -916,7 +916,7 @@
     <t>Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -1089,7 +1089,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
@@ -1109,7 +1109,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1)
+    <t xml:space="preserve">Reference(Encounter)
 </t>
   </si>
   <si>
@@ -1163,7 +1163,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1338,7 +1338,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1367,7 +1367,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
   </si>
   <si>
     <t>Observation.note</t>
@@ -1402,6 +1402,9 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
+    <t>Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
     <t>https://gematik.de/fhir/isik/ValueSet/vs-mii-icu-bodysite-observation-monitoring-und-vitaldaten</t>
   </si>
   <si>
@@ -1420,13 +1423,13 @@
     <t>Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
   </si>
   <si>
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen|4.0.1)
+    <t xml:space="preserve">Reference(Specimen)
 </t>
   </si>
   <si>
@@ -1442,7 +1445,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
+    <t xml:space="preserve">Reference(Device|DeviceMetric)
 </t>
   </si>
   <si>
@@ -1504,7 +1507,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
+    <t xml:space="preserve">Quantity {SimpleQuantity}
 </t>
   </si>
   <si>
@@ -1545,7 +1548,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
   </si>
   <si>
     <t>Observation.referenceRange.appliesTo</t>
@@ -1566,7 +1569,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1597,7 +1600,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1)
+    <t xml:space="preserve">Reference(Observation|QuestionnaireResponse|MolecularSequence)
 </t>
   </si>
   <si>
@@ -1613,7 +1616,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|Observation|4.0.1|MolecularSequence|4.0.1)
+    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|Observation|MolecularSequence)
 </t>
   </si>
   <si>
@@ -2021,7 +2024,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="122.13671875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="94.96484375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -5959,7 +5962,7 @@
         <v>74</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>75</v>
@@ -10423,9 +10426,11 @@
       <c r="X82" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="Y82" s="2"/>
+      <c r="Y82" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="Z82" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>75</v>
@@ -10460,10 +10465,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10489,16 +10494,16 @@
         <v>213</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>366</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>75</v>
@@ -10526,10 +10531,10 @@
         <v>147</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>75</v>
@@ -10547,7 +10552,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>73</v>
@@ -10564,10 +10569,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10590,16 +10595,16 @@
         <v>75</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -10649,7 +10654,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>73</v>
@@ -10666,10 +10671,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10692,16 +10697,16 @@
         <v>75</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -10751,7 +10756,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>73</v>
@@ -10768,10 +10773,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10794,19 +10799,19 @@
         <v>75</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>75</v>
@@ -10855,7 +10860,7 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>73</v>
@@ -10867,15 +10872,15 @@
         <v>75</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10972,10 +10977,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11074,14 +11079,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -11103,10 +11108,10 @@
         <v>102</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>105</v>
@@ -11161,7 +11166,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>73</v>
@@ -11178,10 +11183,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11204,13 +11209,13 @@
         <v>75</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -11261,7 +11266,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>73</v>
@@ -11270,7 +11275,7 @@
         <v>82</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>94</v>
@@ -11278,10 +11283,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11304,13 +11309,13 @@
         <v>75</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -11361,16 +11366,16 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI91" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>94</v>
@@ -11378,10 +11383,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11407,16 +11412,16 @@
         <v>213</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>75</v>
@@ -11444,10 +11449,10 @@
         <v>161</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>75</v>
@@ -11465,7 +11470,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>73</v>
@@ -11482,10 +11487,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11511,16 +11516,16 @@
         <v>213</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>75</v>
@@ -11548,10 +11553,10 @@
         <v>147</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>75</v>
@@ -11569,7 +11574,7 @@
         <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>73</v>
@@ -11586,10 +11591,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11612,17 +11617,17 @@
         <v>75</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>75</v>
@@ -11671,7 +11676,7 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>73</v>
@@ -11688,10 +11693,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11717,10 +11722,10 @@
         <v>96</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -11771,7 +11776,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>73</v>
@@ -11788,10 +11793,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11814,16 +11819,16 @@
         <v>83</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -11873,7 +11878,7 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>73</v>
@@ -11890,10 +11895,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11916,16 +11921,16 @@
         <v>83</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -11975,7 +11980,7 @@
         <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>73</v>
@@ -11992,10 +11997,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12018,19 +12023,19 @@
         <v>83</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>75</v>
@@ -12079,7 +12084,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>73</v>
@@ -12096,10 +12101,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12196,10 +12201,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12298,14 +12303,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -12327,10 +12332,10 @@
         <v>102</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>105</v>
@@ -12385,7 +12390,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>73</v>
@@ -12402,10 +12407,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12431,13 +12436,13 @@
         <v>213</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="O102" t="s" s="2">
         <v>284</v>
@@ -12489,7 +12494,7 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -12506,10 +12511,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12535,13 +12540,13 @@
         <v>369</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M103" t="s" s="2">
         <v>371</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="O103" t="s" s="2">
         <v>373</v>
@@ -12593,7 +12598,7 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>73</v>
@@ -12610,10 +12615,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12639,13 +12644,13 @@
         <v>213</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O104" t="s" s="2">
         <v>416</v>
@@ -12697,7 +12702,7 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>73</v>
@@ -12714,10 +12719,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12801,7 +12806,7 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>73</v>
@@ -12818,10 +12823,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12847,16 +12852,16 @@
         <v>76</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>75</v>
@@ -12905,7 +12910,7 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>73</v>
